--- a/data/Z5.xlsx
+++ b/data/Z5.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="11950" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="实验安排" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="50">
   <si>
     <t>日期</t>
   </si>
@@ -164,6 +164,109 @@
   </si>
   <si>
     <t>B314</t>
+  </si>
+  <si>
+    <r>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>周</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>7-8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>节</t>
+    </r>
+  </si>
+  <si>
+    <t>形势与政策</t>
+  </si>
+  <si>
+    <r>
+      <t>三山楼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>102</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>周</t>
+    </r>
+  </si>
+  <si>
+    <t>三山楼308</t>
+  </si>
+  <si>
+    <r>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>周</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -176,10 +279,15 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -637,153 +745,154 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1317,7 +1426,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -1547,6 +1656,57 @@
         <v>42</v>
       </c>
     </row>
+    <row r="12" spans="1:6">
+      <c r="B12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="B13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="B14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F11" etc:filterBottomFollowUsedRange="0">
     <extLst/>
